--- a/public/data/MASTER_PROGRAM.xlsx
+++ b/public/data/MASTER_PROGRAM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\APP FUAD\Dashboard Rekap Progam Supplier\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{099A4867-FC76-4CDE-A66C-171E81F4D73D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7A0BFEB-761E-40F4-97BE-41C6F0CAACC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" activeTab="3" xr2:uid="{68664D4E-998B-4033-9870-47AD1F913972}"/>
   </bookViews>
